--- a/sim_output_cue.xlsx
+++ b/sim_output_cue.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,348 +513,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>238</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-08-20T00:58:22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cue_plane0_sat0</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-45.2965488608825</v>
-      </c>
-      <c r="E2" t="n">
-        <v>154.1043798374156</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-4018308.115296143</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3572954.559265658</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-4477795.406111979</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4442.650197787064</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-2150.15667187362</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-5706.976510057158</v>
-      </c>
-      <c r="M2" t="n">
-        <v>41.81418089547739</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.5580673603351805</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.4720107983919558</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-41.81200734983336</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1803009413382058</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-08-20T01:05:52</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cue_plane0_sat0</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-54.54815779805525</v>
-      </c>
-      <c r="E3" t="n">
-        <v>153.3219985437715</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1633527.448701163</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2231195.134319589</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-6429114.174639676</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5947.270111672622</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-3695.160551223267</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-2796.376075544893</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.786962101221299</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.3107346220566348</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-18.10368588026464</v>
-      </c>
-      <c r="R3" t="n">
-        <v>59.42072845477508</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-34.70896381063452</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0CD86BD1575B641A929F0115BD08883" ma:contentTypeVersion="11" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="c7f378eef6aae23ec41cafa16c2d4f9c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ddbaa09c-6565-437b-9fe4-1fe08e886c94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e91425144512418e8a3dba2c78bb904b" ns2:_="">
-    <xsd:import namespace="ddbaa09c-6565-437b-9fe4-1fe08e886c94"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ddbaa09c-6565-437b-9fe4-1fe08e886c94" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Afbeeldingtags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b688d343-e684-46db-b94f-a4cae8ed196c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhoudstype"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddbaa09c-6565-437b-9fe4-1fe08e886c94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7CB6DAF-11D1-41A3-A1F5-5E6CF5E7D468}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{220AA09D-944C-4AB0-85FA-B76B54CBA7A6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D3A34C2-11F3-4E72-B1A7-0811F67C8828}"/>
 </file>